--- a/光伏配储项目/电价数据/2026/金砂站.xlsx
+++ b/光伏配储项目/电价数据/2026/金砂站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33573</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38456</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7525299999999999</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.34816</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.37892</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.33388</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.32798</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.32419</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.32069</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.31648</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.32012</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.32371</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.33496</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.31786</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32234</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33633</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.32873</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.28629</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.28475</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.31474</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.35347</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07551000000000001</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.7711699999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.67504</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17326</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26959</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.25913</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24382</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.6556900000000001</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.45548</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.31186</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.31551</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.31455</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.6127</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.5934199999999999</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.78279</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.17437</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39669</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43568</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44291</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.67743</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.89593</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.5630499999999999</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.27345</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.54533</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.0575</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.05593</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.355</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.3635</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.77967</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.42863</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.77013</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8320299999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.78234</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.71975</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.48061</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.445</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.39882</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.40756</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7012</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.51491</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.8836900000000001</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.75254</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.8188</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.47632</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.4893</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.4824</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.48293</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.4673</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.45106</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.36844</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.31957</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.36622</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.31889</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.34699</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38514</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.34184</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.37149</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.49945</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.35499</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36288</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.32451</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.36397</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.53826</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.5379299999999999</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.66849</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.6296799999999999</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9095299999999999</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.30252</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.35903</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.33158</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.34266</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.8759600000000001</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.75158</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.53853</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.44123</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.38798</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.39654</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.42419</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.7221799999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.38368</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>1.48857</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6994400000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>1.201</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.58944</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.68166</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.36273</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.15251</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.62333</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.34326</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.63532</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.06574</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.3279</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.14155</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.22832</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.13241</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.12366</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.9477599999999999</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.26707</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.05724</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4809</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.95094</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.91053</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.45216</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4715299999999999</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37638</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33369</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50784</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48684</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48283</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36947</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.43214</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40412</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.36006</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38248</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.37551</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.41569</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.42925</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33324</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.38652</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36167</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35075</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.36837</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.3839</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.45638</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43585</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.42623</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.3454100000000001</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39187</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35202</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.1645</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.20208</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.12382</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.9058099999999999</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.73356</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.37479</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.7212799999999999</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>1.01347</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.01119</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1.06494</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1.01144</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.25678</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.78646</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.7982</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.81592</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.06818</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5976699999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.6703</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>1.05597</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.00398</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.76712</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.86912</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.5644</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>1.14847</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.6189600000000001</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.43192</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45794</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51401</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.5575599999999999</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.8129299999999999</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.87222</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.7517200000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.69709</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.68306</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.7023400000000001</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.51451</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5446299999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.67888</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.92087</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.81338</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.41206</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.4879</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.67508</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.50349</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.69348</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.9326</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>1.14461</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.75002</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.36338</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.89081</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.6449</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.57578</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.71602</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.45951</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4836</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.41173</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3412</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.48974</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.47118</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.42379</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.38009</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.37927</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.35731</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36007</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33404</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.3371</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.34631</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.37847</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.37903</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34299</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.40946</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.42854</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.45039</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35734</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44248</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34396</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.35231</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32806</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.54276</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35371</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.8803799999999999</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.47914</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.4644</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.42685</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.29012</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.76249</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.44319</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.41256</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.47545</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.8845499999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34518</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.67152</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.51069</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.47171</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.7065900000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.37505</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.4138</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.8978400000000001</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.34695</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.8620599999999999</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.76214</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45065</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.56596</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.60724</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.7110299999999999</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9463400000000001</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.6405700000000001</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.6636599999999999</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.68072</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.65413</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50251</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.5580499999999999</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.52274</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.51071</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4955</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.41932</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31248</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31664</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32216</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.39572</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37398</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31885</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31823</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31871</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31681</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31193</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31816</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.3157799999999999</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30994</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31452</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31968</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30011</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31873</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31361</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31884</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28906</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.29968</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.14337</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02411</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.4078</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.47804</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.2667</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.24105</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10611</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.31862</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.28157</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.02955</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26344</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30053</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32617</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.34873</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36492</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.4272</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36625</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4228</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31698</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.29959</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.23938</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.24594</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.26263</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32721</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.19047</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.18659</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.248</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31701</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.19723</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.24764</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.21401</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.19177</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32741</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.17308</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30514</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.24851</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.20021</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.26677</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.09562999999999999</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.03920000000000001</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00996</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20611</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04922</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19388</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.009310000000000001</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06025</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05846</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35029</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34686</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.31563</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.43923</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31164</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.36813</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31462</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28102</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.42587</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.39067</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.44554</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48565</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.45434</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7881699999999999</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88748</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8703099999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.6534500000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57208</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.43467</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41373</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.3533</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37781</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.39798</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37438</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32189</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.31442</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44362</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.46286</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5817100000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6313099999999999</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.93929</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.59793</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.43856</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.47713</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.819</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.36759</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>1.05448</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.29066</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.31429</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.2656</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.84054</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.6830499999999999</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.35207</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32561</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31892</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30392</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.28486</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31536</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29317</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29592</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29458</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30529</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.17823</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26199</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27642</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28065</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.2914</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.30795</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30024</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30141</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30166</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.30623</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.30128</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.28944</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32327</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.80443</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.30729</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.32859</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31504</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31213</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30303</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.30521</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.30782</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30927</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.29913</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.29994</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.296</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.31358</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.29854</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29715</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.29719</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.29666</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29906</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.3161600000000001</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29176</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29571</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30511</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30336</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.33502</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.47596</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.35925</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.35078</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3391</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.69116</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45443</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.5596</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.33359</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.22571</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.36099</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.37108</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.3598</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.36266</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.59785</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.64159</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.50818</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.47353</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.53389</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.51632</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.40346</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.50234</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.7243999999999999</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.57035</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.52716</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.5763200000000001</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.5702999999999999</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.29869</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.32299</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34067</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34498</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.34924</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32583</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.48988</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.5676599999999999</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.33595</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.39697</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.32211</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.31791</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.38558</v>
+      </c>
+      <c r="C126" t="n">
+        <v>1.32068</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.0216</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.9489500000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.67157</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.86875</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.39208</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5048899999999999</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.31904</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.31961</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.3079</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.39836</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42576</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.32014</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.3107</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.31775</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39076</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.3292</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40058</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.30868</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.3978</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.31837</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.59911</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33285</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.26645</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.4115</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.31557</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31608</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.5112099999999999</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.48797</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.27956</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.31689</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.16606</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29088</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.28871</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.38029</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30069</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.32777</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.38867</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.41743</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.39846</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.40418</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.49699</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31897</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.45641</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.37295</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.36563</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36221</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.31499</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35284</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.44856</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.44541</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31282</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.30745</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.34849</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.31003</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.30321</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.30158</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30597</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.30698</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.28968</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.19511</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.21083</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.18593</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.2056</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.18317</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.17412</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.26473</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.28569</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27671</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.26842</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.43059</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.45245</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.32089</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.04325</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.18557</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.04624</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.30283</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.20511</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.30374</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.37079</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.18062</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.23842</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.24984</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.24548</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.28624</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.30583</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.29261</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.31572</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.28958</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28333</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.29519</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26823</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.28468</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.30455</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.27025</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.29608</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.28547</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.29789</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.29405</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.29502</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28045</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30259</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29172</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.31081</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.30671</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.30568</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.30836</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.39758</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.4187</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39853</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.286</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.24833</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.28069</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.30538</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.30398</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30013</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.30276</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.34119</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.33327</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.30534</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.30299</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.30461</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.30288</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29543</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.29896</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.29995</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.29501</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.2905</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30096</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29436</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.31071</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33031</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3019</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.2848</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28389</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.39396</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30176</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.28675</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.29307</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.2796</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30023</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31521</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31544</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.24762</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.28691</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.28852</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.2878500000000001</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.32515</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.32552</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.3088399999999999</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.33042</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.37809</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.31708</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.3166</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.43473</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2944</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.35706</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.31348</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.31041</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.28735</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.30306</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.30759</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.29651</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.33643</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30363</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.28706</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29236</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.28608</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.29179</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29322</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.29712</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.2949</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.3127799999999999</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.30823</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29299</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.30955</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30505</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29563</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29539</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.28861</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.3085</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31291</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33603</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.39873</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.03314</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.41216</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6418400000000001</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3862</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.48117</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.48861</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43164</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42494</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.38962</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.54112</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.30631</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.44314</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.35686</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.4432</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.75876</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.58135</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.47338</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.43299</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.41209</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.39741</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.52942</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.41363</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.43737</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.4282</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.42863</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36483</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.48666</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.45304</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.55045</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34698</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.77386</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.44705</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.42214</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.51749</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.52458</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.71945</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47459</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.31991</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28438</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.32101</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38407</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.27995</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.28087</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.19738</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.18968</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27783</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.27651</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.2739</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27764</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27775</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27356</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.19147</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.18884</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.15227</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.23449</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.28979</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.18857</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.19429</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.20098</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.16519</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.15667</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.25293</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.31461</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.38078</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.32604</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.32969</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.26452</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31979</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.2961</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32095</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32488</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31398</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.3227</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.37425</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.42172</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.43993</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.34279</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.33621</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.31933</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.28622</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.27881</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31597</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.29359</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.32825</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.27306</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.32944</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.28496</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33084</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.28832</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.25124</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34569</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.27877</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.34779</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.24352</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.23339</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32062</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.29206</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32018</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3202</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32115</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.31983</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28012</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.31918</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31604</v>
+      </c>
+      <c r="L131" t="n">
+        <v>-0.0198</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.28851</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.2849</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27309</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.30937</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.30983</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.2851</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.28237</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29417</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.2824700000000001</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.28302</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28484</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27243</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28369</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.27986</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27362</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28345</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29242</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27348</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28418</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.2701</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29103</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31631</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30091</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31142</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30575</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.3701</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31808</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30547</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32277</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30273</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.3197</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32395</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32304</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.32942</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.31992</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3185</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32404</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39502</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34559</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.57989</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.5133</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.32973</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.20321</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.3399</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29628</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32199</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38095</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34609</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33185</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32264</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31188</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32592</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.32961</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28326</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.32987</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33568</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32628</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32168</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.32772</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31785</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.4044</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31633</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.31982</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.31687</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.33429</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.32467</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31304</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32716</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31929</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3196</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33575</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32817</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32685</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33012</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.3328</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.40844</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.38733</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34031</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.43892</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.49651</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6081799999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5717000000000001</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6170599999999999</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.75851</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.39676</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.47512</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40082</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42917</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.34158</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.32186</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.31602</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31385</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.32748</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.32637</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.34305</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.31937</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.31795</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.31845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.33239</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.30954</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.30867</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.28635</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30254</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.30993</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.29394</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.28059</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.29579</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.30741</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.3088</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.31107</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4487</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.40055</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.43965</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.47056</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.509</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.57582</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40436</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.33254</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32566</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37917</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.35188</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34461</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.66659</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.4064700000000001</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.72834</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.48428</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.3621</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.33954</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33464</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33207</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.46498</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.3474100000000001</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.32388</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33471</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34613</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.33364</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.33694</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33379</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.32139</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.42606</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.33884</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.32324</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.67328</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.55044</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64227</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.31959</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.31464</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32138</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.32437</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.31704</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39421</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.26458</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.28591</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31131</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.30734</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30415</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>-0.00594</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.27481</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28312</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.27478</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.2819700000000001</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29076</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.49211</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36035</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.36923</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.32177</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35085</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32447</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.32813</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.50612</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.49592</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.38197</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.52034</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.53953</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.37852</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.41781</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39038</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.42641</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42583</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42053</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.34755</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.32444</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35265</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.37655</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.48552</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38728</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37346</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37788</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.50596</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.34635</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.37806</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.3663</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37826</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33155</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.25939</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.30885</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.27719</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.33197</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.22644</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31751</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.32711</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.28886</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.23108</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.16487</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-0.00758</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.27083</v>
+      </c>
+      <c r="L135" t="n">
+        <v>-0.01036</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-0.00983</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.16511</v>
+      </c>
+      <c r="O135" t="n">
+        <v>-0.02148</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.19847</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.16391</v>
+      </c>
+      <c r="S135" t="n">
+        <v>-0.01034</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.1546</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.15908</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.19438</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.15675</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.16212</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>-0.01086</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.1648</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>-0.01097</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.03637</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.17558</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.18038</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.14716</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.04198</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32377</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.16385</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.31935</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.32894</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.21165</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.34277</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.72273</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.33423</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>8.000000000000001e-05</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.33118</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.34672</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.39273</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.32171</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.32565</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.35587</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31295</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.31465</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.24941</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3455299999999999</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.34311</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.34034</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.33519</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.2177</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.28502</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.32602</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.26927</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.26737</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.21781</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.22318</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.26945</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.21071</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.30466</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.22863</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.31449</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.22774</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.29166</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27217</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.03768999999999999</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.18292</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.17998</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="L136" t="n">
+        <v>-0.02041</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.19986</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.2211</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.21266</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.03222999999999999</v>
+      </c>
+      <c r="R136" t="n">
+        <v>-0.01816</v>
+      </c>
+      <c r="S136" t="n">
+        <v>-0.01817</v>
+      </c>
+      <c r="T136" t="n">
+        <v>-0.01852</v>
+      </c>
+      <c r="U136" t="n">
+        <v>-0.01852</v>
+      </c>
+      <c r="V136" t="n">
+        <v>-0.01831</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.19448</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.03247</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>-0.01852</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>-0.01849</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.17305</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.03222999999999999</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.03222</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30405</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>-0.01745</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>-0.01657</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24392</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.02303</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00776</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00038</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.24634</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02206</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.00259</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04298</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.0409</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02936</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04365</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.02555</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.30217</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04914</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.02241</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>0.05727</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.02919</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.25421</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.29701</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.3075</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.3226</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>-0.01757</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.32713</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.34964</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.3392</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28035</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.31109</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.31373</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29258</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.33161</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.32621</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32357</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30317</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29134</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31165</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.2983</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.26766</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.31676</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.00223</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.27561</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.277</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.16575</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31757</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.16087</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.16518</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1626</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.04418</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.15873</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.14782</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.04384</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.04473</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>-0.01183</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>-0.0094</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41428</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.18922</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.27483</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.04442</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.23268</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.29981</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.8572000000000001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.86226</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09021999999999999</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.01761</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24709</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28144</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.5277999999999999</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00251</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00178</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31673</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.31402</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06920999999999999</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30841</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.3027</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29188</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47528</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32547</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.32914</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.3144</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32188</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.6270800000000001</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.50044</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.73405</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.86372</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.57076</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.42042</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.70904</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.73737</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.7356</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.73905</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.821</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35574</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.41483</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.36598</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.31796</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3064</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.31066</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.44665</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.30302</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.26764</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.26176</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.1871</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.25728</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.25192</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.21271</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.25313</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.19931</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.1636</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.19494</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.15819</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.16083</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.04474</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.15353</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.17812</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.22878</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.30877</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.27757</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.2382</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.24728</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29724</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25108</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.30268</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3209</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.2994</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32542</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.28665</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30939</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.32019</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30863</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25864</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31132</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30225</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31818</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32831</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.32027</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31379</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.33326</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.32784</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.37421</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.33706</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.32054</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39702</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.33509</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.32919</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.30943</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31258</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.3061</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29462</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.28934</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29016</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.35178</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33152</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32878</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32941</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31194</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31414</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32126</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30107</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.2931</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.29916</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.29923</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30082</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31162</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.3117799999999999</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.30169</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.31446</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31126</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.33135</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.54423</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.41521</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33128</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.33684</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33289</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33253</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33046</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33295</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32509</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32822</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33268</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32197</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.44825</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.41368</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.4532</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.20404</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.74281</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.7537200000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40515</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.5123300000000001</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.63918</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.78184</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.56337</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.37035</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.33793</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.4243</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.33192</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32157</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35453</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.33382</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.32756</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32584</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33085</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.19987</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.30662</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31553</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.31768</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.38485</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.33408</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32032</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31501</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34515</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.31857</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.31685</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31469</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30424</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30077</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.29866</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.29663</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29251</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32038</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29198</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.30163</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.31774</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39096</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.3444700000000001</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37964</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34202</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.3529</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3420299999999999</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3412</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33671</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34193</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34416</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.33735</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34243</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.34953</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.3524</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.34802</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.38783</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.37317</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.50337</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.51775</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.06797</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.7779299999999999</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.5485800000000001</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.71135</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.4747</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.57075</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.51418</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.68426</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.63861</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.00248</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.7495599999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.65487</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5530700000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.39543</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.32852</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.31869</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.32014</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.2834100000000001</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.32951</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.30871</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29432</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.28807</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.29822</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32325</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.28919</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.30359</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3124</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.04632</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.28784</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28215</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31371</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.28897</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.28001</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35564</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33402</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30368</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.3021</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31257</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.30629</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32206</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32632</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35458</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.36558</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.26649</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.42715</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.40983</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5496599999999999</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.33802</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.19882</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.41512</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.32775</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.29753</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.3134</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43474</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.51873</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.3426</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.32122</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.36712</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.35341</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.34271</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34328</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.5407000000000001</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.59746</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33527</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.34446</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39721</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.79238</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.35528</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.82647</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.79414</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.62425</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.44345</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40147</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.45756</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.55584</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39317</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.47049</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.4084</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42148</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.3615</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.32418</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32406</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34292</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.65783</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.43554</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.41448</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.40551</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.33719</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.35974</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.33409</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.3375</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.33499</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.33709</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33762</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.33272</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.32752</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.3332</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.32885</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.32513</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32433</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34007</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33452</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.35576</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.35619</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.35513</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.32773</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.3343</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.30917</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38369</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.27682</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.3875</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.44969</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30414</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.32586</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32328</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35383</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.34632</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.38714</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.41348</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>1.08263</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>1.12512</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.6406900000000001</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.8494299999999999</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>1.22838</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.48035</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38611</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.45199</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.43564</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.7016</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.7870499999999999</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4208</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.43304</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.41739</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.43596</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.42383</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43032</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.41156</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.39191</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.34211</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33691</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.33801</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33764</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36695</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.30588</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35803</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34192</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.3385</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.34206</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.33942</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34684</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.31705</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35529</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33648</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.32731</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.32854</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.324</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.32992</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30517</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.3186</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17611</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29577</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31177</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14577</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19867</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14656</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04788000000000001</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12175</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22625</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26017</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14551</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22686</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.33142</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.19776</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.3702</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.21178</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.34304</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.23617</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.23489</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.40708</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.54474</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.50988</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.42189</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.52063</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>1.07203</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1.22155</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.7461599999999999</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.8372200000000001</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.9671799999999999</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.55624</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.50889</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.5714600000000001</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.44953</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.38067</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.03006</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.9033099999999999</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>1.1579</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>1.22362</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.50956</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>1.09567</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.51823</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>1.03074</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>1.08412</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.79147</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.5136799999999999</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.50466</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.43627</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.47826</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38809</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37215</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36763</v>
       </c>
     </row>
   </sheetData>
